--- a/data/trans_orig/IP16B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16B_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48764</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54256</t>
+          <t>54285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>50634</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57209</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101940</t>
+          <t>101318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110089</t>
+          <t>110095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146133</t>
+          <t>146217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154682</t>
+          <t>154909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173947</t>
+          <t>173740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178362</t>
+          <t>178357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>322642</t>
+          <t>323542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>332017</t>
+          <t>332261</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171146</t>
+          <t>171120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201117</t>
+          <t>201685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208357</t>
+          <t>208347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374614</t>
+          <t>374432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>381039</t>
+          <t>381047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267905</t>
+          <t>268274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>294758</t>
+          <t>294795</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>301528</t>
+          <t>301245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>565382</t>
+          <t>565781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>572708</t>
+          <t>572832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>641840</t>
+          <t>641857</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>651686</t>
+          <t>651919</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>730668</t>
+          <t>730188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>741879</t>
+          <t>741701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1375720</t>
+          <t>1375972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1391436</t>
+          <t>1391602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17180</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>32644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16B_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44931</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41697</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47019</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>83,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>52215</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>48741</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>54285</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>93,31%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54363</t>
+          <t>47402</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50634</t>
+          <t>44295</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>49063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>106577</t>
+          <t>92333</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101318</t>
+          <t>88333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110095</t>
+          <t>95236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4995</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2907</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8229</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1675</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7219</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49926</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49926</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49926</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>55960</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>55960</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>55960</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60668</t>
+          <t>50680</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60668</t>
+          <t>50680</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60668</t>
+          <t>50680</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116627</t>
+          <t>100606</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116627</t>
+          <t>100606</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116627</t>
+          <t>100606</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>153402</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>150794</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>154543</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>151670</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>146217</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>154909</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>92,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>177047</t>
+          <t>138642</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173740</t>
+          <t>133353</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178357</t>
+          <t>141484</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>328716</t>
+          <t>292044</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>323542</t>
+          <t>286544</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>332261</t>
+          <t>295032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4050</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5562</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11015</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154844</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154844</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154844</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>157232</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>157232</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>157232</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178717</t>
+          <t>143621</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178717</t>
+          <t>143621</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178717</t>
+          <t>143621</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>335949</t>
+          <t>298465</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>335949</t>
+          <t>298465</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335949</t>
+          <t>298465</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>194222</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>190045</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>196099</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>99,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>172693</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>171120</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>174334</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>172710</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>206484</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>201685</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>208347</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>469</t>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>379179</t>
+          <t>368556</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374432</t>
+          <t>364036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>381047</t>
+          <t>370434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2180</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6357</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2235</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7034</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>196402</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>196402</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>196402</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>208719</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>208719</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>208719</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>381792</t>
+          <t>371074</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>381792</t>
+          <t>371074</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>381792</t>
+          <t>371074</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,74 +1749,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>286412</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>282302</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>288450</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>271076</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>268274</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>271768</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>252042</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>248408</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>252813</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>299288</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>294795</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>301245</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>671</t>
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>570363</t>
+          <t>538453</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>565781</t>
+          <t>533715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>572832</t>
+          <t>540731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2996</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3494</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4405</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3193</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7686</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>289408</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>289408</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>289408</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>271768</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>271768</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>271768</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>302481</t>
+          <t>252813</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>302481</t>
+          <t>252813</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>302481</t>
+          <t>252813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>574248</t>
+          <t>542221</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>574248</t>
+          <t>542221</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>574248</t>
+          <t>542221</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>678968</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>672766</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>683176</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>647654</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>641857</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>651919</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>612419</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>606483</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>616045</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>97,54%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>737181</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>730188</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>741701</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1384834</t>
+          <t>1291387</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1375972</t>
+          <t>1284136</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1391602</t>
+          <t>1297813</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17814</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>10378</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6113</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16175</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>9367</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5741</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15303</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>13403</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>8883</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>20396</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>43</t>
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>658032</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>658032</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>658032</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621786</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621786</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621786</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1408616</t>
+          <t>1312366</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1408616</t>
+          <t>1312366</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1408616</t>
+          <t>1312366</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
